--- a/CYTK.xlsx
+++ b/CYTK.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shkre\code\models\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0EF44ED-F350-4576-AC80-ADA15133114C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEFA514-1AA9-4BC3-9AE5-D94CCBC94B6C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-31170" yWindow="1860" windowWidth="19845" windowHeight="16215" activeTab="2" xr2:uid="{A49A7A12-B745-4EC9-B913-D708EFED4797}"/>
+    <workbookView xWindow="8980" yWindow="4440" windowWidth="21060" windowHeight="13820" xr2:uid="{A49A7A12-B745-4EC9-B913-D708EFED4797}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="74">
   <si>
     <t>Price</t>
   </si>
@@ -58,9 +58,6 @@
     <t>EV</t>
   </si>
   <si>
-    <t>Q224</t>
-  </si>
-  <si>
     <t>PIC</t>
   </si>
   <si>
@@ -118,9 +115,6 @@
     <t>Phase III "MAPLE-HCM" vs metoprolol</t>
   </si>
   <si>
-    <t>Phase III "ACACIA-HCM"</t>
-  </si>
-  <si>
     <t>Phase III "CEDAR-HCM"</t>
   </si>
   <si>
@@ -133,9 +127,6 @@
     <t>Phase</t>
   </si>
   <si>
-    <t>Filing</t>
-  </si>
-  <si>
     <t>Phase III "FOREST-HCM"</t>
   </si>
   <si>
@@ -146,13 +137,136 @@
   </si>
   <si>
     <t>fast skeletal troponin activator</t>
+  </si>
+  <si>
+    <t>Q126</t>
+  </si>
+  <si>
+    <t>Myqorzo (aficamten)</t>
+  </si>
+  <si>
+    <t>Approved</t>
+  </si>
+  <si>
+    <t>Revenue</t>
+  </si>
+  <si>
+    <t>Q125</t>
+  </si>
+  <si>
+    <t>Q225</t>
+  </si>
+  <si>
+    <t>Q325</t>
+  </si>
+  <si>
+    <t>Q425</t>
+  </si>
+  <si>
+    <t>Q226</t>
+  </si>
+  <si>
+    <t>Q326</t>
+  </si>
+  <si>
+    <t>Q426</t>
+  </si>
+  <si>
+    <t>COGS</t>
+  </si>
+  <si>
+    <t>Gross Profit</t>
+  </si>
+  <si>
+    <t>oHCM</t>
+  </si>
+  <si>
+    <t>Phase III "ACACIA-HCM" nHCM</t>
+  </si>
+  <si>
+    <t>met PE</t>
+  </si>
+  <si>
+    <t>filed</t>
+  </si>
+  <si>
+    <t>CK-089 (CK-4015089)</t>
+  </si>
+  <si>
+    <t>I</t>
+  </si>
+  <si>
+    <t>ulacamten</t>
+  </si>
+  <si>
+    <t>III</t>
+  </si>
+  <si>
+    <t>HFrEF</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Collaboration</t>
+  </si>
+  <si>
+    <t>Net Income</t>
+  </si>
+  <si>
+    <t>EPS</t>
+  </si>
+  <si>
+    <t>Taxes</t>
+  </si>
+  <si>
+    <t>Pretax Income</t>
+  </si>
+  <si>
+    <t>Interest</t>
+  </si>
+  <si>
+    <t>Operating Income</t>
+  </si>
+  <si>
+    <t>Operating Expenses</t>
+  </si>
+  <si>
+    <t>SG&amp;A</t>
+  </si>
+  <si>
+    <t>R&amp;D</t>
+  </si>
+  <si>
+    <t>we will use it more than mavi - Dutch doc</t>
+  </si>
+  <si>
+    <t>RNA/antisense exciting</t>
+  </si>
+  <si>
+    <t>angiotensin inhibitor</t>
+  </si>
+  <si>
+    <t>anticoagulation</t>
+  </si>
+  <si>
+    <t>miRNA</t>
+  </si>
+  <si>
+    <t>chinese LVAD</t>
+  </si>
+  <si>
+    <t>hybrid heart</t>
+  </si>
+  <si>
+    <t>Myqorzo</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color theme="1"/>
@@ -169,6 +283,13 @@
     <font>
       <b/>
       <u/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -282,7 +403,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -300,6 +421,17 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="4" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -318,6 +450,61 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>56807</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>56807</xdr:colOff>
+      <xdr:row>32</xdr:row>
+      <xdr:rowOff>139512</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="3" name="Straight Connector 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{26ED7A5F-0E9A-95D9-FF9F-987DB5D19C8F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5237531" y="0"/>
+          <a:ext cx="0" cy="5193236"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -637,27 +824,27 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{42353201-ED6E-407F-99F1-919EDB88A99D}">
-  <dimension ref="B2:L12"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="B2:L13"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.5703125" customWidth="1"/>
+    <col min="1" max="1" width="4.54296875" customWidth="1"/>
     <col min="2" max="2" width="20" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.28515625" customWidth="1"/>
-    <col min="4" max="4" width="22.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.26953125" customWidth="1"/>
+    <col min="4" max="4" width="22.26953125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B2" s="9" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C2" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>13</v>
-      </c>
       <c r="E2" s="10" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="F2" s="10"/>
       <c r="G2" s="10"/>
@@ -666,94 +853,101 @@
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <v>56.68</v>
-      </c>
-    </row>
-    <row r="3" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B3" s="4" t="s">
-        <v>11</v>
+        <v>76.680000000000007</v>
+      </c>
+    </row>
+    <row r="3" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B3" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>46</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H3" s="5"/>
       <c r="J3" t="s">
         <v>1</v>
       </c>
       <c r="K3" s="3">
-        <v>117.659578</v>
+        <v>132.08600000000001</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B4" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B4" s="15"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D4" t="s">
-        <v>16</v>
-      </c>
-      <c r="H4" s="5"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="11"/>
       <c r="J4" t="s">
         <v>2</v>
       </c>
       <c r="K4" s="3">
         <f>+K2*K3</f>
-        <v>6668.9448810399999</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B5" s="14" t="s">
-        <v>15</v>
+        <v>10128.354480000002</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" t="s">
+        <v>54</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>53</v>
       </c>
       <c r="H5" s="5"/>
       <c r="J5" t="s">
         <v>3</v>
       </c>
       <c r="K5" s="3">
-        <f>190.142+866.633+305.361</f>
-        <v>1362.136</v>
+        <f>1165.686+538.317</f>
+        <v>1704.0029999999999</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>27</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="H6" s="5"/>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6" s="3">
-        <f>11.52+550.6+92.831</f>
-        <v>654.95100000000002</v>
+        <f>248.202+27.358+871.527</f>
+        <v>1147.087</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B7" s="4"/>
-      <c r="C7" t="s">
-        <v>34</v>
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="D7" t="s">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="H7" s="5"/>
       <c r="J7" t="s">
@@ -761,52 +955,72 @@
       </c>
       <c r="K7" s="3">
         <f>+K4-K5+K6</f>
-        <v>5961.7598810400004</v>
-      </c>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+        <v>9571.4384800000007</v>
+      </c>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="4"/>
+      <c r="C8" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" t="s">
+        <v>32</v>
+      </c>
       <c r="H8" s="5"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B9" s="4"/>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D9" t="s">
+        <v>32</v>
+      </c>
+      <c r="E9" t="s">
+        <v>51</v>
+      </c>
       <c r="H9" s="5"/>
       <c r="J9" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="K9" s="3">
         <v>2500.654</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B10" s="4"/>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
+        <v>52</v>
+      </c>
       <c r="H10" s="5"/>
       <c r="J10" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="K10" s="3">
         <v>2391.1990000000001</v>
       </c>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
       <c r="H11" s="5"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B12" s="6"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="8"/>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B12" s="4"/>
+      <c r="H12" s="5"/>
       <c r="J12" t="s">
-        <v>9</v>
-      </c>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="B5" location="aficamten!A1" display="aficamten" xr:uid="{3C39CB6B-3D31-4CC3-9398-EA66DB1877D2}"/>
+    <hyperlink ref="B3" location="aficamten!A1" display="aficamten" xr:uid="{3C39CB6B-3D31-4CC3-9398-EA66DB1877D2}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -814,81 +1028,444 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DB37C984-346A-4931-B9C2-A7ABEF87E26D}">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
-  <sheetData/>
+  <dimension ref="A1:J17"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="4.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="10" width="8.7265625" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="C2" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="16"/>
+      <c r="D3" s="16"/>
+      <c r="E3" s="16"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16">
+        <v>4.7889999999999997</v>
+      </c>
+      <c r="H3" s="16">
+        <v>25</v>
+      </c>
+      <c r="I3" s="16">
+        <f>+H3+25</f>
+        <v>50</v>
+      </c>
+      <c r="J3" s="16">
+        <f>+I3+25</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="C4" s="16"/>
+      <c r="D4" s="16"/>
+      <c r="E4" s="16"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16">
+        <f>2.637+11.929</f>
+        <v>14.566000000000001</v>
+      </c>
+      <c r="H4" s="16">
+        <v>3.29</v>
+      </c>
+      <c r="I4" s="16"/>
+      <c r="J4" s="16"/>
+    </row>
+    <row r="5" spans="1:10" s="17" customFormat="1" ht="13" x14ac:dyDescent="0.3">
+      <c r="B5" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="18"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18">
+        <f>+G3+G4</f>
+        <v>19.355</v>
+      </c>
+      <c r="H5" s="18">
+        <f>+H4+H3</f>
+        <v>28.29</v>
+      </c>
+      <c r="I5" s="18">
+        <f>+I4+I3</f>
+        <v>50</v>
+      </c>
+      <c r="J5" s="18">
+        <f>+J4+J3</f>
+        <v>75</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B6" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16">
+        <f>0.16+2.392</f>
+        <v>2.552</v>
+      </c>
+      <c r="H6" s="16">
+        <f>2.731+2.861</f>
+        <v>5.5920000000000005</v>
+      </c>
+      <c r="I6" s="16">
+        <f>+I5*0.1</f>
+        <v>5</v>
+      </c>
+      <c r="J6" s="16">
+        <f>+J5*0.1</f>
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16">
+        <f>+G5-G6</f>
+        <v>16.803000000000001</v>
+      </c>
+      <c r="H7" s="16">
+        <f>+H5-H6</f>
+        <v>22.698</v>
+      </c>
+      <c r="I7" s="16">
+        <f>+I5-I6</f>
+        <v>45</v>
+      </c>
+      <c r="J7" s="16">
+        <f>+J5-J6</f>
+        <v>67.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16">
+        <v>95.525000000000006</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="16"/>
+    </row>
+    <row r="9" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B9" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16">
+        <v>104.896</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+      <c r="J9" s="16"/>
+    </row>
+    <row r="10" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C10" s="16"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="16"/>
+      <c r="F10" s="16"/>
+      <c r="G10" s="16">
+        <f>+G8+G9</f>
+        <v>200.42099999999999</v>
+      </c>
+      <c r="H10" s="16">
+        <f>+H8+H9</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="16"/>
+      <c r="J10" s="16"/>
+    </row>
+    <row r="11" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="16"/>
+      <c r="G11" s="16">
+        <f>+G7-G10</f>
+        <v>-183.61799999999999</v>
+      </c>
+      <c r="H11" s="16">
+        <f>+H7-H10</f>
+        <v>22.698</v>
+      </c>
+      <c r="I11" s="16"/>
+      <c r="J11" s="16"/>
+    </row>
+    <row r="12" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="16"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="16">
+        <f>-14.519+11.022</f>
+        <v>-3.4969999999999999</v>
+      </c>
+      <c r="H12" s="16"/>
+      <c r="I12" s="16"/>
+      <c r="J12" s="16"/>
+    </row>
+    <row r="13" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B13" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16">
+        <f>+G11+G12</f>
+        <v>-187.11500000000001</v>
+      </c>
+      <c r="H13" s="16">
+        <f>+H11+H12</f>
+        <v>22.698</v>
+      </c>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+    </row>
+    <row r="14" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B14" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16"/>
+      <c r="J14" s="16"/>
+    </row>
+    <row r="15" spans="1:10" s="3" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C15" s="16"/>
+      <c r="D15" s="16"/>
+      <c r="E15" s="16"/>
+      <c r="F15" s="16"/>
+      <c r="G15" s="16">
+        <f>+G13-G14</f>
+        <v>-187.11500000000001</v>
+      </c>
+      <c r="H15" s="16">
+        <f>+H13-H14</f>
+        <v>22.698</v>
+      </c>
+      <c r="I15" s="16"/>
+      <c r="J15" s="16"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="B16" t="s">
+        <v>58</v>
+      </c>
+      <c r="G16" s="19">
+        <f>+G15/G17</f>
+        <v>-1.5166608577241374</v>
+      </c>
+      <c r="H16" s="19">
+        <f>+H15/H17</f>
+        <v>0.17184258740517541</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.25">
+      <c r="B17" t="s">
+        <v>1</v>
+      </c>
+      <c r="G17" s="16">
+        <v>123.373</v>
+      </c>
+      <c r="H17" s="16">
+        <v>132.08600000000001</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{820767BF-BF34-44B5-A34D-0C11A3B98053}">
-  <dimension ref="A1:C19"/>
-  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:D29"/>
+  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B2" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B2" t="s">
+      <c r="C2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B3" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B3" t="s">
+      <c r="C3" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" t="s">
         <v>20</v>
       </c>
-      <c r="C3" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="B5" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="B5" t="s">
+    <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C6" s="13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C6" s="13" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C7" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C7" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="D8" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C10" s="13" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C9" s="13" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C11" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C13" s="13" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="C14" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="C16" s="13" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C12" s="13" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="C15" s="13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="19" spans="3:3" x14ac:dyDescent="0.2">
-      <c r="C19" s="13" t="s">
-        <v>32</v>
+    <row r="20" spans="2:3" ht="13" x14ac:dyDescent="0.3">
+      <c r="C20" s="13" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>72</v>
       </c>
     </row>
   </sheetData>
